--- a/AAII_Financials/Yearly/SSCC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSCC_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Yearly/SSCC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSCC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>SSCC</t>
   </si>
@@ -690,16 +690,16 @@
         <v>44561</v>
       </c>
       <c r="G7" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H7" s="2">
         <v>40543</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>40178</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>39813</v>
-      </c>
-      <c r="J7" s="2">
-        <v>39447</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -710,23 +710,23 @@
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3"/>
     </row>
@@ -855,8 +855,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>200</v>
@@ -864,11 +864,11 @@
       <c r="F14" s="3">
         <v>-600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>-100</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
@@ -923,22 +923,22 @@
         <v>5400</v>
       </c>
       <c r="E17" s="3">
-        <v>32400</v>
+        <v>32200</v>
       </c>
       <c r="F17" s="3">
-        <v>48700</v>
+        <v>49300</v>
       </c>
       <c r="G17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="H17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>500</v>
       </c>
       <c r="K17" s="3"/>
     </row>
@@ -946,26 +946,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-5400</v>
       </c>
       <c r="E18" s="3">
-        <v>-32400</v>
+        <v>-32200</v>
       </c>
       <c r="F18" s="3">
-        <v>-48700</v>
+        <v>-49300</v>
       </c>
       <c r="G18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-500</v>
       </c>
       <c r="K18" s="3"/>
     </row>
@@ -986,26 +986,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3"/>
     </row>
@@ -1014,25 +1014,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5600</v>
+        <v>-5300</v>
       </c>
       <c r="E21" s="3">
-        <v>-32300</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-32100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-600</v>
       </c>
       <c r="K21" s="3"/>
     </row>
@@ -1040,8 +1040,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1049,8 +1049,8 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>500</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
@@ -1077,16 +1077,16 @@
         <v>-48700</v>
       </c>
       <c r="G23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-500</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -1094,26 +1094,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -1158,16 +1158,16 @@
         <v>-48700</v>
       </c>
       <c r="G26" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-500</v>
       </c>
       <c r="K26" s="3"/>
     </row>
@@ -1185,16 +1185,16 @@
         <v>-48700</v>
       </c>
       <c r="G27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-500</v>
       </c>
       <c r="K27" s="3"/>
     </row>
@@ -1229,23 +1229,23 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>4</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1310,26 +1310,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3"/>
     </row>
@@ -1347,16 +1347,16 @@
         <v>-48700</v>
       </c>
       <c r="G33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-500</v>
       </c>
       <c r="K33" s="3"/>
     </row>
@@ -1401,16 +1401,16 @@
         <v>-48700</v>
       </c>
       <c r="G35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-500</v>
       </c>
       <c r="K35" s="3"/>
     </row>
@@ -1433,16 +1433,16 @@
         <v>44561</v>
       </c>
       <c r="G38" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H38" s="2">
         <v>40543</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>40178</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>39813</v>
-      </c>
-      <c r="J38" s="2">
-        <v>39447</v>
       </c>
       <c r="K38" s="2"/>
     </row>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41" s="3">
         <v>0</v>
@@ -1512,17 +1512,17 @@
       <c r="F42" s="3">
         <v>0</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3"/>
     </row>
@@ -1539,17 +1539,17 @@
       <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3"/>
     </row>
@@ -1563,8 +1563,8 @@
       <c r="E44" s="3">
         <v>500</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
@@ -1584,26 +1584,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>700</v>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3"/>
     </row>
@@ -1621,16 +1621,16 @@
         <v>100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46" s="3">
         <v>0</v>
       </c>
       <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
         <v>100</v>
-      </c>
-      <c r="J46" s="3">
-        <v>700</v>
       </c>
       <c r="K46" s="3"/>
     </row>
@@ -1638,26 +1638,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3"/>
     </row>
@@ -1785,11 +1785,11 @@
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -1837,16 +1837,16 @@
         <v>700</v>
       </c>
       <c r="G54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H54" s="3">
         <v>0</v>
       </c>
       <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
         <v>100</v>
-      </c>
-      <c r="J54" s="3">
-        <v>800</v>
       </c>
       <c r="K54" s="3"/>
     </row>
@@ -1890,16 +1890,16 @@
         <v>500</v>
       </c>
       <c r="G57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1300</v>
+        <v>400</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I57" s="3">
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
         <v>1100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1200</v>
       </c>
       <c r="K57" s="3"/>
     </row>
@@ -1908,25 +1908,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
-        <v>300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>200</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3"/>
     </row>
@@ -1935,25 +1935,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3"/>
     </row>
@@ -1971,16 +1971,16 @@
         <v>1200</v>
       </c>
       <c r="G60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1200</v>
       </c>
       <c r="K60" s="3"/>
     </row>
@@ -1989,16 +1989,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2016,13 +2016,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>500</v>
+        <v>700</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
@@ -2133,16 +2133,16 @@
         <v>1700</v>
       </c>
       <c r="G66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1200</v>
       </c>
       <c r="K66" s="3"/>
     </row>
@@ -2281,16 +2281,16 @@
         <v>-54900</v>
       </c>
       <c r="G72" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="H72" s="3">
         <v>-7500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-6500</v>
       </c>
       <c r="K72" s="3"/>
     </row>
@@ -2389,16 +2389,16 @@
         <v>-1000</v>
       </c>
       <c r="G76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H76" s="3">
         <v>-1500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-500</v>
       </c>
       <c r="K76" s="3"/>
     </row>
@@ -2448,16 +2448,16 @@
         <v>44561</v>
       </c>
       <c r="G80" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H80" s="2">
         <v>40543</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>40178</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>39813</v>
-      </c>
-      <c r="J80" s="2">
-        <v>39447</v>
       </c>
       <c r="K80" s="2"/>
     </row>
@@ -2475,16 +2475,16 @@
         <v>-48700</v>
       </c>
       <c r="G81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-500</v>
       </c>
       <c r="K81" s="3"/>
     </row>
@@ -2506,13 +2506,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>4</v>
@@ -2680,13 +2680,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-100</v>
       </c>
       <c r="K89" s="3"/>
     </row>
@@ -2708,7 +2708,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
@@ -2946,7 +2946,7 @@
         <v>200</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
@@ -2963,26 +2963,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3"/>
     </row>
@@ -3000,16 +3000,16 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-100</v>
       </c>
       <c r="K102" s="3"/>
     </row>
